--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1520,6 +1520,123 @@
       <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115947405</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137283352</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99429</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mollaryd Tomtahagen 1, Dalhem, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>383267</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6419830</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Herrljunga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Molla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-07-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Berggren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Berggren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137283352</t>
         </is>
       </c>
     </row>
@@ -1532,6 +1649,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1625,12 +1625,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Berggren</t>
+          <t>Elin Wendt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Berggren</t>
+          <t>Elin Wendt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 11881-2023 artfynd.xlsx
+++ b/artfynd/A 11881-2023 artfynd.xlsx
@@ -1528,7 +1528,7 @@
         <v>137283352</v>
       </c>
       <c r="B9" t="n">
-        <v>99469</v>
+        <v>99473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
